--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-19T22:42:49.435Z</t>
+    <t>2026-05-19T22:57:13.202Z</t>
   </si>
   <si>
     <t>Home - Lottabody</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-19T22:57:13.202Z</t>
+    <t>2026-05-19T23:14:42.521Z</t>
   </si>
   <si>
     <t>Home - Lottabody</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-19T23:14:42.521Z</t>
+    <t>2026-05-19T23:22:17.808Z</t>
   </si>
   <si>
     <t>Home - Lottabody</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-19T23:22:17.808Z</t>
+    <t>2026-05-19T23:42:02.488Z</t>
   </si>
   <si>
     <t>Home - Lottabody</t>
